--- a/PageObjectModelFramework/resources/testdata.xlsx
+++ b/PageObjectModelFramework/resources/testdata.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
   <si>
     <t>browser</t>
   </si>
@@ -230,17 +230,43 @@
     <t>NewCarsBrandViewPage</t>
   </si>
   <si>
-    <t>BasePage intialies the constaructur whose argumrent is webdriver driver. Also object of Key as well as carbase Page are also initialized</t>
+    <t>BMW Cars</t>
+  </si>
+  <si>
+    <t>query</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>BasePage intializes the constructur whose argumrent is webdriver driver. Also object of Keyword as well as carbase Page are also initialized</t>
+  </si>
+  <si>
+    <t>https://www.carwale.com/kia-cars/sonet/</t>
+  </si>
+  <si>
+    <t>pageUrl</t>
+  </si>
+  <si>
+    <t>select * from kiasonetwebtable</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -284,10 +310,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -300,8 +327,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -614,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -622,9 +651,11 @@
     <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -646,8 +677,14 @@
       <c r="G1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -669,19 +706,25 @@
       <c r="G2" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
+        <v>70</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>11</v>
@@ -693,12 +736,12 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
         <v>17</v>
@@ -716,12 +759,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
         <v>16</v>
@@ -740,6 +783,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="I2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1146,7 +1192,7 @@
     </row>
     <row r="18" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C18" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="20" spans="3:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
